--- a/data/trans_dic/P37A$otros-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37A$otros-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -727,37 +727,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,7</t>
+          <t>0,16; 1,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,15</t>
+          <t>0,28; 1,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,48</t>
+          <t>0,06; 0,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,16</t>
+          <t>0,3; 1,04</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,58</t>
+          <t>0,05; 0,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,64</t>
+          <t>0,1; 0,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,16</t>
+          <t>0,41; 1,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,6</t>
+          <t>0,06; 0,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,73</t>
+          <t>0,1; 0,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,57</t>
+          <t>0,75; 1,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,3</t>
+          <t>0,05; 0,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,33</t>
+          <t>0,05; 0,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,56</t>
+          <t>0,16; 0,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,18</t>
+          <t>0,69; 1,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,32</t>
+          <t>0,29; 2,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,78</t>
+          <t>0,97; 3,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,75</t>
+          <t>0,16; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,17</t>
+          <t>0,71; 2,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,54</t>
+          <t>0,36; 1,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,6</t>
+          <t>0,98; 2,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,26</t>
+          <t>0,03; 0,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,19</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,66</t>
+          <t>0,2; 0,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,32</t>
+          <t>0,62; 1,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,3</t>
+          <t>0,03; 0,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,35</t>
+          <t>0,06; 0,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,57</t>
+          <t>0,16; 0,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,31</t>
+          <t>0,76; 1,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,06; 0,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,21</t>
+          <t>0,05; 0,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,53</t>
+          <t>0,22; 0,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,19</t>
+          <t>0,77; 1,28</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8132</t>
         </is>
       </c>
     </row>
@@ -1514,52 +1514,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5320</t>
+          <t>0; 5559</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>875; 8756</t>
+          <t>911; 9684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8568</t>
+          <t>0; 8184</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6250</t>
+          <t>0; 6722</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6178</t>
+          <t>0; 6788</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1782; 8695</t>
+          <t>2331; 9348</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7921</t>
+          <t>0; 8524</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 5859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>969; 8309</t>
+          <t>967; 9136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4180; 14753</t>
+          <t>4208; 14515</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>41757</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1028; 9880</t>
+          <t>882; 8205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6782</t>
+          <t>0; 5819</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2104; 13308</t>
+          <t>2118; 12939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9172; 26636</t>
+          <t>9061; 28000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5289</t>
+          <t>0; 5292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1024; 10507</t>
+          <t>1024; 10714</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2517; 14575</t>
+          <t>2011; 13247</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13496; 35098</t>
+          <t>16260; 37570</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1744; 9905</t>
+          <t>1738; 11254</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234; 12332</t>
+          <t>1987; 12244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6890; 22577</t>
+          <t>6346; 20817</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25116; 53448</t>
+          <t>30180; 58964</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>22144</t>
         </is>
       </c>
     </row>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1391; 12696</t>
+          <t>1577; 13290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5375; 24465</t>
+          <t>6935; 25967</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5305</t>
+          <t>0; 5946</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,17 +1950,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>870; 9622</t>
+          <t>880; 9551</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4455; 14304</t>
+          <t>5208; 15988</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6403</t>
+          <t>0; 5877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3406; 16912</t>
+          <t>3926; 18307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12709; 33972</t>
+          <t>14194; 34189</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>880; 8415</t>
+          <t>876; 8839</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6638</t>
+          <t>0; 6737</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6317; 22326</t>
+          <t>6719; 22661</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19177; 45696</t>
+          <t>21831; 47772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>986; 10156</t>
+          <t>984; 10786</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2115; 12369</t>
+          <t>2018; 12038</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5789; 20045</t>
+          <t>5576; 19860</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24677; 48035</t>
+          <t>28162; 53975</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3806; 15158</t>
+          <t>3725; 15682</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3028; 14495</t>
+          <t>3168; 14358</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15616; 36427</t>
+          <t>15420; 37771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49356; 84647</t>
+          <t>55604; 92587</t>
         </is>
       </c>
     </row>
